--- a/outputs/34033.xlsx
+++ b/outputs/34033.xlsx
@@ -612,7 +612,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="9.65"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="10.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -646,7 +646,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="10.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="n">
         <v>44927</v>
       </c>
@@ -666,7 +666,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="10.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="n">
         <v>44958</v>
       </c>
@@ -695,7 +695,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="10.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="n">
         <v>44986</v>
       </c>
@@ -712,7 +712,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="10.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7"/>
       <c r="B6" s="8"/>
       <c r="C6" s="9"/>
@@ -728,11 +728,11 @@
         <v>44968</v>
       </c>
       <c r="K6" s="14" t="n">
-        <f aca="false">IF($I6="Parameter 1",LOOKUP(2,1/(($B$3:$B$13=$H6)*($A$3:$A$13&lt;=$J6)),$C$3:$C$13),IF($I6="Parameter 2",LOOKUP(2,1/(($B$3:$B$13=$H6)*($A$3:$A$13&lt;=$J6)),$D$3:$D$13),LOOKUP(2,1/(($B$3:$B$13=$H6)*($A$3:$A$13&lt;=$J6)),$E$3:$E$13)))</f>
+        <f aca="true">INDEX($C$3:$E$13,MATCH($H6,$B$3:$B$13,0)+MATCH($J6,OFFSET($A$3:$A$13,MATCH($H6,$B$3:$B$13,0)-1,0,COUNTIF($B$3:$B$13,$H6),1),1)-1,MATCH($I6,$C$1:$E$1,0))</f>
         <v>26</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="10.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="n">
         <v>44936</v>
       </c>
@@ -758,11 +758,11 @@
         <v>44938</v>
       </c>
       <c r="K7" s="14" t="n">
-        <f aca="false">IF($I7="Parameter 1",LOOKUP(2,1/(($B$3:$B$13=$H7)*($A$3:$A$13&lt;=$J7)),$C$3:$C$13),IF($I7="Parameter 2",LOOKUP(2,1/(($B$3:$B$13=$H7)*($A$3:$A$13&lt;=$J7)),$D$3:$D$13),LOOKUP(2,1/(($B$3:$B$13=$H7)*($A$3:$A$13&lt;=$J7)),$E$3:$E$13)))</f>
+        <f aca="true">INDEX($C$3:$E$13,MATCH($H7,$B$3:$B$13,0)+MATCH($J7,OFFSET($A$3:$A$13,MATCH($H7,$B$3:$B$13,0)-1,0,COUNTIF($B$3:$B$13,$H7),1),1)-1,MATCH($I7,$C$1:$E$1,0))</f>
         <v>250</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="10.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="n">
         <v>44967</v>
       </c>
@@ -788,11 +788,11 @@
         <v>45010</v>
       </c>
       <c r="K8" s="14" t="n">
-        <f aca="false">IF($I8="Parameter 1",LOOKUP(2,1/(($B$3:$B$13=$H8)*($A$3:$A$13&lt;=$J8)),$C$3:$C$13),IF($I8="Parameter 2",LOOKUP(2,1/(($B$3:$B$13=$H8)*($A$3:$A$13&lt;=$J8)),$D$3:$D$13),LOOKUP(2,1/(($B$3:$B$13=$H8)*($A$3:$A$13&lt;=$J8)),$E$3:$E$13)))</f>
+        <f aca="true">INDEX($C$3:$E$13,MATCH($H8,$B$3:$B$13,0)+MATCH($J8,OFFSET($A$3:$A$13,MATCH($H8,$B$3:$B$13,0)-1,0,COUNTIF($B$3:$B$13,$H8),1),1)-1,MATCH($I8,$C$1:$E$1,0))</f>
         <v>5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="10.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="n">
         <v>44995</v>
       </c>
@@ -818,11 +818,11 @@
         <v>44982</v>
       </c>
       <c r="K9" s="14" t="n">
-        <f aca="false">IF($I9="Parameter 1",LOOKUP(2,1/(($B$3:$B$13=$H9)*($A$3:$A$13&lt;=$J9)),$C$3:$C$13),IF($I9="Parameter 2",LOOKUP(2,1/(($B$3:$B$13=$H9)*($A$3:$A$13&lt;=$J9)),$D$3:$D$13),LOOKUP(2,1/(($B$3:$B$13=$H9)*($A$3:$A$13&lt;=$J9)),$E$3:$E$13)))</f>
+        <f aca="true">INDEX($C$3:$E$13,MATCH($H9,$B$3:$B$13,0)+MATCH($J9,OFFSET($A$3:$A$13,MATCH($H9,$B$3:$B$13,0)-1,0,COUNTIF($B$3:$B$13,$H9),1),1)-1,MATCH($I9,$C$1:$E$1,0))</f>
         <v>301</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="10.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7"/>
       <c r="B10" s="8"/>
       <c r="C10" s="9"/>
@@ -838,11 +838,11 @@
         <v>45112</v>
       </c>
       <c r="K10" s="14" t="n">
-        <f aca="false">IF($I10="Parameter 1",LOOKUP(2,1/(($B$3:$B$13=$H10)*($A$3:$A$13&lt;=$J10)),$C$3:$C$13),IF($I10="Parameter 2",LOOKUP(2,1/(($B$3:$B$13=$H10)*($A$3:$A$13&lt;=$J10)),$D$3:$D$13),LOOKUP(2,1/(($B$3:$B$13=$H10)*($A$3:$A$13&lt;=$J10)),$E$3:$E$13)))</f>
+        <f aca="true">INDEX($C$3:$E$13,MATCH($H10,$B$3:$B$13,0)+MATCH($J10,OFFSET($A$3:$A$13,MATCH($H10,$B$3:$B$13,0)-1,0,COUNTIF($B$3:$B$13,$H10),1),1)-1,MATCH($I10,$C$1:$E$1,0))</f>
         <v>95</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="10.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="n">
         <v>44946</v>
       </c>
@@ -859,7 +859,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="10.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="n">
         <v>44977</v>
       </c>
@@ -876,7 +876,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="10.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="n">
         <v>45005</v>
       </c>
